--- a/backend/templates/excel/plantilla_3.xlsx
+++ b/backend/templates/excel/plantilla_3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecnologicodeantioquia-my.sharepoint.com/personal/paola_garcia44_correo_tdea_edu_co/Documents/Escritorio/Automatización geotecnica/automatizacion_geotecnica/backend/templates/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{91CFB531-908F-46FD-B5E4-2E392237C245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{91CFB531-908F-46FD-B5E4-2E392237C245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16CF5EF1-A11A-45F5-B677-227377410085}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="6150" yWindow="4050" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="P3" sheetId="50" r:id="rId1"/>
@@ -415,7 +415,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -499,6 +499,13 @@
       <sz val="7"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="1"/>
+      <charset val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -587,7 +594,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -673,47 +680,50 @@
     <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="17" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1119,7 +1129,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:S51"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.5703125" customWidth="1"/>
     <col min="2" max="2" width="9.5703125" customWidth="1"/>
@@ -1141,184 +1151,184 @@
     <col min="18" max="18" width="2.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="38" t="s">
+    <row r="2" spans="1:19">
+      <c r="A2" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
-      <c r="O2" s="38"/>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="38"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="38" t="s">
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="33"/>
+      <c r="Q2" s="33"/>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="A3" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
-      <c r="L3" s="38"/>
-      <c r="M3" s="38"/>
-      <c r="N3" s="38"/>
-      <c r="O3" s="38"/>
-      <c r="P3" s="38"/>
-      <c r="Q3" s="38"/>
-    </row>
-    <row r="4" spans="1:19" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="39"/>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="39"/>
-      <c r="K4" s="39"/>
-      <c r="L4" s="39"/>
-      <c r="M4" s="39"/>
-      <c r="N4" s="39"/>
-      <c r="O4" s="39"/>
-      <c r="P4" s="39"/>
-      <c r="Q4" s="39"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5" s="40" t="s">
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="33"/>
+      <c r="L3" s="33"/>
+      <c r="M3" s="33"/>
+      <c r="N3" s="33"/>
+      <c r="O3" s="33"/>
+      <c r="P3" s="33"/>
+      <c r="Q3" s="33"/>
+    </row>
+    <row r="4" spans="1:19" ht="9.75" customHeight="1">
+      <c r="A4" s="34"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="34"/>
+      <c r="N4" s="34"/>
+      <c r="O4" s="34"/>
+      <c r="P4" s="34"/>
+      <c r="Q4" s="34"/>
+    </row>
+    <row r="5" spans="1:19">
+      <c r="A5" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="33" t="s">
+      <c r="B5" s="35"/>
+      <c r="C5" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="33"/>
-      <c r="M5" s="33"/>
-      <c r="N5" s="33"/>
-      <c r="O5" s="33"/>
-      <c r="P5" s="33"/>
-      <c r="Q5" s="33"/>
-    </row>
-    <row r="6" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="40" t="s">
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="36"/>
+      <c r="K5" s="36"/>
+      <c r="L5" s="36"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+    </row>
+    <row r="6" spans="1:19" ht="24" customHeight="1">
+      <c r="A6" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="41" t="s">
+      <c r="B6" s="35"/>
+      <c r="C6" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="41"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="41"/>
-      <c r="N6" s="41"/>
-      <c r="O6" s="41"/>
-      <c r="P6" s="41"/>
-      <c r="Q6" s="41"/>
-    </row>
-    <row r="7" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="43" t="s">
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="37"/>
+      <c r="I6" s="37"/>
+      <c r="J6" s="37"/>
+      <c r="K6" s="37"/>
+      <c r="L6" s="37"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="37"/>
+      <c r="O6" s="37"/>
+      <c r="P6" s="37"/>
+      <c r="Q6" s="37"/>
+    </row>
+    <row r="7" spans="1:19" ht="15" customHeight="1">
+      <c r="A7" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="43"/>
-      <c r="C7" s="32">
+      <c r="B7" s="39"/>
+      <c r="C7" s="42">
         <v>39379</v>
       </c>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="34" t="s">
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="34"/>
+      <c r="G7" s="40"/>
       <c r="H7" s="11">
         <v>63.5</v>
       </c>
       <c r="I7" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="35" t="s">
+      <c r="J7" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="K7" s="35"/>
-      <c r="L7" s="36" t="s">
+      <c r="K7" s="43"/>
+      <c r="L7" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="M7" s="36"/>
-      <c r="N7" s="42" t="s">
+      <c r="M7" s="44"/>
+      <c r="N7" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="O7" s="42"/>
-      <c r="P7" s="42"/>
-      <c r="Q7" s="42"/>
-    </row>
-    <row r="8" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="43" t="s">
+      <c r="O7" s="38"/>
+      <c r="P7" s="38"/>
+      <c r="Q7" s="38"/>
+    </row>
+    <row r="8" spans="1:19" ht="15" customHeight="1">
+      <c r="A8" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="43"/>
-      <c r="C8" s="33" t="s">
+      <c r="B8" s="39"/>
+      <c r="C8" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="33"/>
+      <c r="D8" s="36"/>
       <c r="E8" s="4"/>
-      <c r="F8" s="34" t="s">
+      <c r="F8" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="34"/>
+      <c r="G8" s="40"/>
       <c r="H8" s="11">
         <v>0.76</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="J8" s="35"/>
-      <c r="K8" s="35"/>
-      <c r="L8" s="36"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="42" t="s">
+      <c r="J8" s="43"/>
+      <c r="K8" s="43"/>
+      <c r="L8" s="44"/>
+      <c r="M8" s="44"/>
+      <c r="N8" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="O8" s="42"/>
-      <c r="P8" s="42"/>
-      <c r="Q8" s="42"/>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="O8" s="38"/>
+      <c r="P8" s="38"/>
+      <c r="Q8" s="38"/>
+    </row>
+    <row r="9" spans="1:19">
       <c r="A9" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="45" t="s">
         <v>25</v>
       </c>
       <c r="C9" s="9" t="s">
@@ -1367,7 +1377,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="15" customHeight="1">
       <c r="A10" s="1">
         <v>0.45</v>
       </c>
@@ -1432,7 +1442,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="15" customHeight="1">
       <c r="A11" s="1">
         <v>1.45</v>
       </c>
@@ -1486,18 +1496,18 @@
         <f>0.32*(K11*45/55+15)</f>
         <v>10.896107128491304</v>
       </c>
-      <c r="O11" s="37">
+      <c r="O11" s="32">
         <v>5</v>
       </c>
       <c r="P11" s="27">
         <f t="shared" ref="P11:P35" si="10">L11</f>
         <v>32.060093238554664</v>
       </c>
-      <c r="Q11" s="44" t="s">
+      <c r="Q11" s="31" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="14.45" customHeight="1">
       <c r="A12" s="1">
         <v>2.4500000000000002</v>
       </c>
@@ -1551,14 +1561,14 @@
         <f t="shared" ref="N12:N16" si="12">0.32*(K12*45/55+15)</f>
         <v>13.64264552792703</v>
       </c>
-      <c r="O12" s="37"/>
+      <c r="O12" s="32"/>
       <c r="P12" s="27">
         <f t="shared" si="10"/>
         <v>35.546895548912133</v>
       </c>
-      <c r="Q12" s="44"/>
-    </row>
-    <row r="13" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q12" s="31"/>
+    </row>
+    <row r="13" spans="1:19" ht="15" customHeight="1">
       <c r="A13" s="1">
         <v>3.45</v>
       </c>
@@ -1612,14 +1622,14 @@
         <f t="shared" si="12"/>
         <v>14.876089887166113</v>
       </c>
-      <c r="O13" s="37"/>
+      <c r="O13" s="32"/>
       <c r="P13" s="27">
         <f t="shared" si="10"/>
         <v>36.933155706959795</v>
       </c>
-      <c r="Q13" s="44"/>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q13" s="31"/>
+    </row>
+    <row r="14" spans="1:19">
       <c r="A14" s="1">
         <v>4.45</v>
       </c>
@@ -1673,17 +1683,17 @@
         <f t="shared" si="12"/>
         <v>15.485045291818832</v>
       </c>
-      <c r="O14" s="37"/>
+      <c r="O14" s="32"/>
       <c r="P14" s="27">
         <f t="shared" si="10"/>
         <v>37.586206210449191</v>
       </c>
-      <c r="Q14" s="44"/>
+      <c r="Q14" s="31"/>
       <c r="S14">
         <v>0.217</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="14.45" customHeight="1">
       <c r="A15" s="1">
         <v>5.45</v>
       </c>
@@ -1737,14 +1747,14 @@
         <f t="shared" si="12"/>
         <v>16.327178432024105</v>
       </c>
-      <c r="O15" s="37"/>
+      <c r="O15" s="32"/>
       <c r="P15" s="27">
         <f t="shared" si="10"/>
         <v>38.459384482098599</v>
       </c>
-      <c r="Q15" s="44"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q15" s="31"/>
+    </row>
+    <row r="16" spans="1:19">
       <c r="A16" s="1">
         <v>6.45</v>
       </c>
@@ -1798,14 +1808,14 @@
         <f t="shared" si="12"/>
         <v>15.458208857714364</v>
       </c>
-      <c r="O16" s="37"/>
+      <c r="O16" s="32"/>
       <c r="P16" s="27">
         <f t="shared" si="10"/>
         <v>37.557824753654131</v>
       </c>
-      <c r="Q16" s="44"/>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q16" s="31"/>
+    </row>
+    <row r="17" spans="1:17">
       <c r="A17" s="1">
         <v>7.45</v>
       </c>
@@ -1864,9 +1874,9 @@
         <f t="shared" si="10"/>
         <v>37.914659077131461</v>
       </c>
-      <c r="Q17" s="44"/>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q17" s="31"/>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18" s="1">
         <v>8.4499999999999993</v>
       </c>
@@ -1925,9 +1935,9 @@
         <f t="shared" si="10"/>
         <v>37.585637030977693</v>
       </c>
-      <c r="Q18" s="44"/>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q18" s="31"/>
+    </row>
+    <row r="19" spans="1:17">
       <c r="A19" s="1">
         <v>9.4499999999999993</v>
       </c>
@@ -1986,9 +1996,9 @@
         <f t="shared" si="10"/>
         <v>37.730302550959522</v>
       </c>
-      <c r="Q19" s="44"/>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q19" s="31"/>
+    </row>
+    <row r="20" spans="1:17">
       <c r="A20" s="1">
         <v>10.45</v>
       </c>
@@ -2047,9 +2057,9 @@
         <f t="shared" si="10"/>
         <v>37.667422234367464</v>
       </c>
-      <c r="Q20" s="44"/>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q20" s="31"/>
+    </row>
+    <row r="21" spans="1:17">
       <c r="A21" s="1">
         <v>11.45</v>
       </c>
@@ -2108,9 +2118,9 @@
         <f t="shared" si="10"/>
         <v>37.814389609430989</v>
       </c>
-      <c r="Q21" s="44"/>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q21" s="31"/>
+    </row>
+    <row r="22" spans="1:17">
       <c r="A22" s="1">
         <v>12.45</v>
       </c>
@@ -2169,9 +2179,9 @@
         <f t="shared" si="10"/>
         <v>37.76563042125477</v>
       </c>
-      <c r="Q22" s="44"/>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q22" s="31"/>
+    </row>
+    <row r="23" spans="1:17">
       <c r="A23" s="1">
         <v>13.45</v>
       </c>
@@ -2230,9 +2240,9 @@
         <f t="shared" si="10"/>
         <v>37.906163842370248</v>
       </c>
-      <c r="Q23" s="44"/>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q23" s="31"/>
+    </row>
+    <row r="24" spans="1:17">
       <c r="A24" s="1">
         <v>14.45</v>
       </c>
@@ -2291,9 +2301,9 @@
         <f t="shared" si="10"/>
         <v>37.862990650569699</v>
       </c>
-      <c r="Q24" s="44"/>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q24" s="31"/>
+    </row>
+    <row r="25" spans="1:17">
       <c r="A25" s="1">
         <v>15.45</v>
       </c>
@@ -2352,9 +2362,9 @@
         <f t="shared" si="10"/>
         <v>37.480245408046173</v>
       </c>
-      <c r="Q25" s="44"/>
-    </row>
-    <row r="26" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q25" s="31"/>
+    </row>
+    <row r="26" spans="1:17" ht="15" customHeight="1">
       <c r="A26" s="1">
         <v>16.45</v>
       </c>
@@ -2413,9 +2423,9 @@
         <f t="shared" si="10"/>
         <v>37.116066658036587</v>
       </c>
-      <c r="Q26" s="44"/>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q26" s="31"/>
+    </row>
+    <row r="27" spans="1:17">
       <c r="A27" s="1">
         <v>17.45</v>
       </c>
@@ -2474,9 +2484,9 @@
         <f t="shared" si="10"/>
         <v>36.768299291370468</v>
       </c>
-      <c r="Q27" s="44"/>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q27" s="31"/>
+    </row>
+    <row r="28" spans="1:17">
       <c r="A28" s="1">
         <v>18.45</v>
       </c>
@@ -2535,9 +2545,9 @@
         <f t="shared" si="10"/>
         <v>36.435142398032269</v>
       </c>
-      <c r="Q28" s="44"/>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q28" s="31"/>
+    </row>
+    <row r="29" spans="1:17">
       <c r="A29" s="1">
         <v>19.45</v>
       </c>
@@ -2596,9 +2606,9 @@
         <f t="shared" si="10"/>
         <v>36.115074748395962</v>
       </c>
-      <c r="Q29" s="44"/>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q29" s="31"/>
+    </row>
+    <row r="30" spans="1:17">
       <c r="A30" s="1">
         <v>20.45</v>
       </c>
@@ -2657,9 +2667,9 @@
         <f t="shared" si="10"/>
         <v>35.806798975681815</v>
       </c>
-      <c r="Q30" s="44"/>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q30" s="31"/>
+    </row>
+    <row r="31" spans="1:17">
       <c r="A31" s="1">
         <v>21.45</v>
       </c>
@@ -2718,9 +2728,9 @@
         <f t="shared" si="10"/>
         <v>35.509199079409626</v>
       </c>
-      <c r="Q31" s="44"/>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q31" s="31"/>
+    </row>
+    <row r="32" spans="1:17">
       <c r="A32" s="1">
         <v>22.45</v>
       </c>
@@ -2779,9 +2789,9 @@
         <f t="shared" si="10"/>
         <v>35.221307596463504</v>
       </c>
-      <c r="Q32" s="44"/>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q32" s="31"/>
+    </row>
+    <row r="33" spans="1:17">
       <c r="A33" s="1">
         <v>23.45</v>
       </c>
@@ -2840,9 +2850,9 @@
         <f t="shared" si="10"/>
         <v>34.942279906638539</v>
       </c>
-      <c r="Q33" s="44"/>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q33" s="31"/>
+    </row>
+    <row r="34" spans="1:17">
       <c r="A34" s="1">
         <v>24.45</v>
       </c>
@@ -2901,9 +2911,9 @@
         <f t="shared" si="10"/>
         <v>34.671373883099491</v>
       </c>
-      <c r="Q34" s="44"/>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q34" s="31"/>
+    </row>
+    <row r="35" spans="1:17">
       <c r="A35" s="1">
         <v>25.45</v>
       </c>
@@ -2962,9 +2972,9 @@
         <f t="shared" si="10"/>
         <v>34.407933601957566</v>
       </c>
-      <c r="Q35" s="44"/>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q35" s="31"/>
+    </row>
+    <row r="36" spans="1:17">
       <c r="A36" s="16"/>
       <c r="B36" s="19"/>
       <c r="C36" s="16"/>
@@ -2983,7 +2993,7 @@
       <c r="P36" s="25"/>
       <c r="Q36" s="26"/>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17">
       <c r="A37" s="16"/>
       <c r="B37" s="19"/>
       <c r="C37" s="16"/>
@@ -3002,7 +3012,7 @@
       <c r="P37" s="25"/>
       <c r="Q37" s="26"/>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17">
       <c r="A38" s="16"/>
       <c r="B38" s="19"/>
       <c r="C38" s="16"/>
@@ -3021,7 +3031,7 @@
       <c r="P38" s="25"/>
       <c r="Q38" s="26"/>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17">
       <c r="A39" s="16"/>
       <c r="B39" s="19"/>
       <c r="C39" s="16"/>
@@ -3040,7 +3050,7 @@
       <c r="P39" s="25"/>
       <c r="Q39" s="26"/>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17">
       <c r="A40" s="16"/>
       <c r="B40" s="19"/>
       <c r="C40" s="16"/>
@@ -3059,7 +3069,7 @@
       <c r="P40" s="25"/>
       <c r="Q40" s="26"/>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17">
       <c r="A41" s="16"/>
       <c r="B41" s="19"/>
       <c r="C41" s="16"/>
@@ -3078,7 +3088,7 @@
       <c r="P41" s="25"/>
       <c r="Q41" s="26"/>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17">
       <c r="A42" s="16"/>
       <c r="B42" s="19"/>
       <c r="C42" s="16"/>
@@ -3097,7 +3107,7 @@
       <c r="P42" s="25"/>
       <c r="Q42" s="26"/>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17">
       <c r="A43" s="16"/>
       <c r="B43" s="19"/>
       <c r="C43" s="16"/>
@@ -3116,7 +3126,7 @@
       <c r="P43" s="25"/>
       <c r="Q43" s="26"/>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17">
       <c r="A44" s="16"/>
       <c r="B44" s="19"/>
       <c r="C44" s="16"/>
@@ -3135,40 +3145,45 @@
       <c r="P44" s="25"/>
       <c r="Q44" s="26"/>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17">
       <c r="A45" s="16"/>
       <c r="Q45" s="13"/>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A46" s="31" t="s">
+    <row r="46" spans="1:17">
+      <c r="A46" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="B46" s="31"/>
+      <c r="B46" s="41"/>
       <c r="Q46" s="13"/>
     </row>
-    <row r="48" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" ht="15.75" thickBot="1">
       <c r="A48" s="17"/>
       <c r="B48" s="17"/>
       <c r="C48" s="17"/>
       <c r="D48" s="17"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1">
       <c r="A49" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1">
       <c r="A50" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1">
       <c r="A51" t="s">
         <v>36</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="J7:K8"/>
+    <mergeCell ref="L7:M8"/>
     <mergeCell ref="Q11:Q35"/>
     <mergeCell ref="O11:O16"/>
     <mergeCell ref="A2:Q2"/>
@@ -3184,11 +3199,6 @@
     <mergeCell ref="F8:G8"/>
     <mergeCell ref="N8:Q8"/>
     <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="J7:K8"/>
-    <mergeCell ref="L7:M8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="122" scale="97" orientation="landscape" r:id="rId1"/>
